--- a/artfynd/A 34418-2023 artfynd.xlsx
+++ b/artfynd/A 34418-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34418-2023 artfynd.xlsx
+++ b/artfynd/A 34418-2023 artfynd.xlsx
@@ -3514,7 +3514,7 @@
         <v>121087392</v>
       </c>
       <c r="B27" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>121087391</v>
       </c>
       <c r="B28" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 34418-2023 artfynd.xlsx
+++ b/artfynd/A 34418-2023 artfynd.xlsx
@@ -3514,7 +3514,7 @@
         <v>121087392</v>
       </c>
       <c r="B27" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
